--- a/Partial-Entries-Converted-to-Apps/06-29-26-westernunion-partials-converted-to-apps-this-week.xlsx
+++ b/Partial-Entries-Converted-to-Apps/06-29-26-westernunion-partials-converted-to-apps-this-week.xlsx
@@ -415,13 +415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.9" customWidth="1" min="1" max="1"/>
-    <col width="20.9" customWidth="1" min="2" max="2"/>
-    <col width="20.9" customWidth="1" min="3" max="3"/>
-    <col width="36.3" customWidth="1" min="4" max="4"/>
+    <col width="23.1" customWidth="1" min="2" max="2"/>
+    <col width="19.8" customWidth="1" min="3" max="3"/>
+    <col width="39.6" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -455,621 +455,567 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>003QP00001aGxer</t>
+          <t>003QP00001c0ygv</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Sajad</t>
+          <t>Naman</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Rasool</t>
+          <t>Garg</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>sajadrasool9@gmail.com</t>
+          <t>naman.garg@youthyatra.com</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-22-2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0033h00001Hf0j4</t>
+          <t>0033h0000187BtJ</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Elvis</t>
+          <t>Nelly</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Kadhama</t>
+          <t>Kininga</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>essymartafrica@gmail.com</t>
+          <t>nellyhapp12@gmail.com</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b9wGf</t>
+          <t>003QP00000AmBOP</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Umar</t>
+          <t>Chizoba</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Nzeakor</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>abutaimiyyah04@gmail.com</t>
+          <t>hannyrapheal@gmail.com</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>06-16-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bBaDd</t>
+          <t>003QP00001cBbyl</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Emmanuel</t>
+          <t>Dalila</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Entonu</t>
+          <t>Sumani Zakari</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>emmanuel.entonu@cobwebtel.com</t>
+          <t>sumanlila43@gmail.com</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>06-16-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bEXb1</t>
+          <t>003QP00001c7WrZ</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Adwoa</t>
+          <t>Kafayat</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Owusu</t>
+          <t>Tiamiyu</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>awuraadwoaowusu@gmail.com</t>
+          <t>tiamiyukafayat.work@gmail.com</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>06-16-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b9LU1</t>
+          <t>003QP00001aZmN3</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Niraj</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>PATTA</t>
+          <t>Borate</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>pattagrace1@gmail.com</t>
+          <t>nirajborateindia@gmail.com</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>06-16-2026</t>
+          <t>06-24-2026</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b9M6p</t>
+          <t>003QP00000vfvxc</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Jose Rei</t>
+          <t>Meghna</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Lunda</t>
+          <t>Joshi</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>lundaj@africau.edu</t>
+          <t>swanlivelihood@gmail.com</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>06-16-2026</t>
+          <t>06-24-2026</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>003QP00001YrnTA</t>
+          <t>003QP00001cIK8W</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Njock</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Porton</t>
+          <t>Mokum</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>porton.victor@gmail.com</t>
+          <t>njockmokum@gmail.com</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>06-16-2026</t>
+          <t>06-24-2026</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>003QP00000mMM7v</t>
+          <t>003QP00001SycnD</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Prince</t>
+          <t>Hellen</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Nyong</t>
+          <t>Lunkuse</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>nyongprince0@gmail.com</t>
+          <t>hellentanyinga@gmail.com</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>06-17-2026</t>
+          <t>06-25-2026</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bUPPl</t>
+          <t>003QP00001cS6nI</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Buntu</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Drane</t>
+          <t>Hlotywa</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>info@sawasawausa.com</t>
+          <t>buntuhlotywa@gmail.com</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>06-17-2026</t>
+          <t>06-25-2026</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>003QP00001beKVN</t>
+          <t>003QP00001cdREt</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>GERVASIO OBIANG</t>
+          <t>Nkechinyere Melva</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>OVONO MELE</t>
+          <t>Uguru</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>conegamuerte@gmail.com</t>
+          <t>uguruiyoku@gmail.com</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-26-2026</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bWV9O</t>
+          <t>003QP00001UXzcP</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Mrs YOSSA MARIA</t>
+          <t>Festus</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>EPSE NDJENGOUE</t>
+          <t>Afolayan</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>rafrohorizon10@gmail.com</t>
+          <t>festusafolayan02@gmail.com</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-26-2026</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>003QP00000BH1JW</t>
+          <t>003QP00001cdqJh</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Muhammed</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>Canaoay</t>
+          <t>Faraz</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>chestercanaoay93@gmail.com</t>
+          <t>frarzfazal2000@gmail.com</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-26-2026</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bXnx1</t>
+          <t>003QP00000ApOAb</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Madhuree</t>
+          <t>Ahmed Ali</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Shahane</t>
+          <t>Saleh</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>admin@edignite.org</t>
+          <t>ahmadalisaleh5@gmail.com</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-26-2026</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bVZ6v</t>
+          <t>003QP00001coLZ7</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Bishwadeep</t>
+          <t>CYNTHIA</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>Moitra</t>
+          <t>THOMAS</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>info@silaiwali.com</t>
+          <t>thomasreply@yahoo.com</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-27-2026</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bgG4A</t>
+          <t>003QP00000lyg7o</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Fauzy</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>Emetumah</t>
+          <t>Ihekweme</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>fauzy.emetumah@gmail.com</t>
+          <t>ruby.ihekweme@digitaleydrive.com</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>06-19-2026</t>
+          <t>06-27-2026</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bgjAz</t>
+          <t>003QP00001SPYYd</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Clemency</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>Ishaya</t>
+          <t>Kpwang Abbe</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>iclemencyzere@gmail.com</t>
+          <t>kabbenis@gmail.com</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>06-19-2026</t>
+          <t>06-27-2026</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bidz8</t>
+          <t>003QP00001corVt</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Alheri</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>Sekani</t>
+          <t>Oluwatimilehin</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>alherisekani@gmail.com</t>
+          <t>oluwatimilehinjoshua08@gmail.com</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>06-19-2026</t>
+          <t>06-27-2026</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bggHx</t>
+          <t>003QP00001cqlkP</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>CHINEDU</t>
+          <t>Bella</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>NDIMELE</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>markndimele@gmail.com</t>
+          <t>bella@livingoutside.org</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>06-19-2026</t>
+          <t>06-28-2026</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>003QP00000BH17y</t>
+          <t>003QP00001crwnR</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Daria</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>Daguanno</t>
+          <t>Kutsko</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>fernando@alquimetricos.cc</t>
+          <t>dariakutsko@gmail.com</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>06-20-2026</t>
+          <t>06-28-2026</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bqqJP</t>
+          <t>003QP00001cu4c2</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>Benevolent</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>Nzveda</t>
+          <t>Mike-Akwudi</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>gavinbee75@gmail.com</t>
+          <t>sharonchukwuoma20@gmail.com</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>06-20-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>003QP00001bs8fY</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>Mohd Khalid</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>Naseemi</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>khalidnaseemi@gmail.com</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>06-20-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>003QP00001bp5Cl</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>Élisabeth</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>OTEMAKOFE ELAYI</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>ongdapesp@gmail.com</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>06-20-2026</t>
+          <t>06-28-2026</t>
         </is>
       </c>
     </row>
